--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9D39314-ACEC-4E37-AA9D-A4652E28BF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73AB5FD9-DEED-4B64-8032-0EC92052BC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73AB5FD9-DEED-4B64-8032-0EC92052BC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BB5AB18-FBDC-4EF3-9408-E06E53FEF4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BB5AB18-FBDC-4EF3-9408-E06E53FEF4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF5CEA9B-A691-4CBC-A1D1-5F3E77C56D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF5CEA9B-A691-4CBC-A1D1-5F3E77C56D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46858E50-86CF-4E40-B438-19DDD4C3E3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46858E50-86CF-4E40-B438-19DDD4C3E3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7F247A6-AA41-4B20-A184-9841E973BE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7F247A6-AA41-4B20-A184-9841E973BE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48467117-F531-4075-8851-C1BB2C92E1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
